--- a/docs/Packing Lists/Packing List Taller/Packing List Taller Exemple.xlsx
+++ b/docs/Packing Lists/Packing List Taller/Packing List Taller Exemple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\docs\Packing Lists\Packing List Taller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CD4D7C-D69E-46E1-B685-5411EBEFC2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B208B-26A2-419B-B59E-F3879AE9CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="LISTE DE COLIS" sheetId="1" r:id="rId1"/>
     <sheet name="FACTURE" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LISTE DE COLIS'!$A$1:$O$28</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
   <si>
     <t>SWEET BAG SARL</t>
   </si>
@@ -50,6 +53,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>Lot</t>
     </r>
@@ -58,6 +62,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -66,6 +71,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>N</t>
     </r>
@@ -74,6 +80,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>°</t>
     </r>
@@ -82,6 +89,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -90,6 +98,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>230</t>
     </r>
@@ -98,6 +107,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -106,6 +116,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>BIS</t>
     </r>
@@ -114,6 +125,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -122,6 +134,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>An-namae</t>
     </r>
@@ -130,6 +143,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -138,6 +152,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>Bensouda</t>
     </r>
@@ -146,6 +161,7 @@
         <sz val="8"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -154,6 +170,7 @@
         <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Calisto MT"/>
+        <family val="1"/>
       </rPr>
       <t>-FES</t>
     </r>
@@ -165,9 +182,6 @@
     <t>Champ requis</t>
   </si>
   <si>
-    <t>Le format du tableau ne peut pas être modifié. Les lignes ne peuvent pas être fusionnées.</t>
-  </si>
-  <si>
     <t>COLISAGE:</t>
   </si>
   <si>
@@ -177,13 +191,7 @@
     <t>Requis selon client</t>
   </si>
   <si>
-    <t>Si des informations supplémentaires doivent être ajoutées (caisses contenant des articles défectueux, etc.), les ajouter après le tableau.</t>
-  </si>
-  <si>
     <t>DATE :</t>
-  </si>
-  <si>
-    <t>Les références, coleurs et client noms doivent être exactes, avec le « . » dans le cas d’AMI</t>
   </si>
   <si>
     <t>PUNTOTRES
@@ -257,37 +265,10 @@
     <t>CH</t>
   </si>
   <si>
-    <t>61-70</t>
-  </si>
-  <si>
-    <t>71-88</t>
-  </si>
-  <si>
-    <t>89-140</t>
-  </si>
-  <si>
-    <t>PALOMA WOOL</t>
-  </si>
-  <si>
-    <t>MOD.TEST</t>
-  </si>
-  <si>
-    <t>ROUGE</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>APC</t>
   </si>
   <si>
     <t>UST</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>F67008</t>
   </si>
   <si>
     <t>LAW</t>
@@ -306,6 +287,41 @@
   </si>
   <si>
     <t>Poids Net  (Kg)</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>SMS</t>
+  </si>
+  <si>
+    <t>DIMENSIONS 
+CAISSE</t>
+  </si>
+  <si>
+    <t>60X60X40</t>
+  </si>
+  <si>
+    <t>POIDS BRUT
+CAISSE</t>
+  </si>
+  <si>
+    <t>F67008</t>
   </si>
 </sst>
 </file>
@@ -326,11 +342,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -343,16 +361,19 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -361,12 +382,14 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -375,44 +398,53 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calisto MT"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Lustria"/>
     </font>
   </fonts>
   <fills count="4">
@@ -435,7 +467,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -673,11 +705,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -721,9 +803,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -732,9 +811,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -748,14 +824,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -767,18 +836,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -787,12 +844,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -803,7 +854,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -819,6 +870,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1034,19 +1115,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AA1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.28515625" customWidth="1"/>
     <col min="2" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="20.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" customWidth="1"/>
     <col min="10" max="10" width="14.140625" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="27" width="11.5703125" customWidth="1"/>
+    <col min="12" max="14" width="11.5703125" customWidth="1"/>
+    <col min="15" max="15" width="1.140625" customWidth="1"/>
+    <col min="16" max="27" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="13.5" customHeight="1">
@@ -1081,7 +1167,7 @@
     <row r="2" spans="1:27" ht="22.5" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7"/>
@@ -1152,9 +1238,7 @@
       </c>
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="N4" s="11"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1173,23 +1257,21 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="4"/>
       <c r="J5" s="14"/>
       <c r="K5" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="5"/>
       <c r="M5" s="1"/>
-      <c r="N5" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="N5" s="10"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
@@ -1208,7 +1290,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="16">
         <v>45640</v>
@@ -1219,9 +1301,7 @@
       <c r="J6" s="4"/>
       <c r="L6" s="5"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="10" t="s">
-        <v>10</v>
-      </c>
+      <c r="N6" s="10"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
@@ -1265,7 +1345,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27" ht="13.5" customHeight="1">
+    <row r="8" spans="1:27" ht="13.5" customHeight="1" thickBot="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1294,44 +1374,48 @@
       <c r="Z8" s="1"/>
       <c r="AA8" s="1"/>
     </row>
-    <row r="9" spans="1:27" ht="31.5" customHeight="1">
+    <row r="9" spans="1:27" ht="31.5" customHeight="1" thickBot="1">
       <c r="A9" s="4"/>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="F9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="G9" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="H9" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="I9" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="J9" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="K9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="L9" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>19</v>
+      <c r="M9" s="20" t="s">
+        <v>48</v>
       </c>
-      <c r="K9" s="21" t="s">
-        <v>20</v>
+      <c r="N9" s="44" t="s">
+        <v>46</v>
       </c>
-      <c r="L9" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
+      <c r="O9" s="22"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
@@ -1346,38 +1430,44 @@
     </row>
     <row r="10" spans="1:27" ht="21" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26" t="s">
+      <c r="B10" s="23">
+        <v>145</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="G10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="H10" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="I10" s="25"/>
+      <c r="J10" s="24">
+        <v>8</v>
+      </c>
+      <c r="K10" s="24">
+        <v>200</v>
+      </c>
+      <c r="L10" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="27" t="s">
-        <v>26</v>
+      <c r="M10" s="24">
+        <v>10</v>
       </c>
-      <c r="H10" s="27" t="s">
-        <v>27</v>
+      <c r="N10" s="47" t="s">
+        <v>47</v>
       </c>
-      <c r="I10" s="27"/>
-      <c r="J10" s="28">
-        <v>8</v>
-      </c>
-      <c r="K10" s="26">
-        <v>200</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
+      <c r="O10" s="26"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
@@ -1392,38 +1482,44 @@
     </row>
     <row r="11" spans="1:27" ht="21" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="23">
+        <v>145</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="G11" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" s="34" t="s">
+      <c r="H11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35">
+      <c r="I11" s="29"/>
+      <c r="J11" s="28">
         <v>8</v>
       </c>
-      <c r="K11" s="33">
+      <c r="K11" s="28">
         <v>266</v>
       </c>
-      <c r="L11" s="36" t="s">
-        <v>30</v>
+      <c r="L11" s="48" t="s">
+        <v>27</v>
       </c>
-      <c r="M11" s="30"/>
-      <c r="N11" s="31"/>
-      <c r="O11" s="31"/>
+      <c r="M11" s="28">
+        <v>10</v>
+      </c>
+      <c r="N11" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="26"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
@@ -1438,38 +1534,44 @@
     </row>
     <row r="12" spans="1:27" ht="21" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="33" t="s">
-        <v>22</v>
+      <c r="B12" s="23">
+        <v>145</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="34" t="s">
-        <v>31</v>
+      <c r="H12" s="29" t="s">
+        <v>30</v>
       </c>
-      <c r="F12" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="34"/>
-      <c r="J12" s="35">
+      <c r="I12" s="29"/>
+      <c r="J12" s="28">
         <v>8</v>
       </c>
-      <c r="K12" s="33">
-        <v>68</v>
+      <c r="K12" s="28">
+        <v>8</v>
       </c>
-      <c r="L12" s="36" t="s">
-        <v>34</v>
+      <c r="L12" s="48" t="s">
+        <v>39</v>
       </c>
-      <c r="M12" s="30"/>
-      <c r="N12" s="31"/>
-      <c r="O12" s="31"/>
+      <c r="M12" s="28">
+        <v>10</v>
+      </c>
+      <c r="N12" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O12" s="26"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1484,38 +1586,44 @@
     </row>
     <row r="13" spans="1:27" ht="21" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33" t="s">
-        <v>22</v>
+      <c r="B13" s="23">
+        <v>145</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="C13" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>31</v>
+      <c r="H13" s="29" t="s">
+        <v>24</v>
       </c>
-      <c r="F13" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="34"/>
-      <c r="J13" s="35">
+      <c r="I13" s="29"/>
+      <c r="J13" s="28">
         <v>8</v>
       </c>
-      <c r="K13" s="33">
-        <v>130</v>
+      <c r="K13" s="28">
+        <v>8</v>
       </c>
-      <c r="L13" s="36" t="s">
-        <v>35</v>
+      <c r="L13" s="48" t="s">
+        <v>40</v>
       </c>
-      <c r="M13" s="30"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
+      <c r="M13" s="28">
+        <v>8</v>
+      </c>
+      <c r="N13" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O13" s="26"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
@@ -1530,38 +1638,44 @@
     </row>
     <row r="14" spans="1:27" ht="21" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="33" t="s">
-        <v>22</v>
+      <c r="B14" s="23">
+        <v>145</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="C14" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="34" t="s">
+      <c r="H14" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H14" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="35">
+      <c r="I14" s="29"/>
+      <c r="J14" s="28">
         <v>8</v>
       </c>
-      <c r="K14" s="33">
-        <v>406</v>
+      <c r="K14" s="28">
+        <v>8</v>
       </c>
-      <c r="L14" s="36" t="s">
-        <v>36</v>
+      <c r="L14" s="48" t="s">
+        <v>41</v>
       </c>
-      <c r="M14" s="30"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
+      <c r="M14" s="28">
+        <v>8</v>
+      </c>
+      <c r="N14" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O14" s="26"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
@@ -1576,36 +1690,46 @@
     </row>
     <row r="15" spans="1:27" ht="21" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="33" t="s">
-        <v>37</v>
+      <c r="B15" s="27">
+        <v>144</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="C15" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="34" t="s">
-        <v>38</v>
+      <c r="H15" s="29" t="s">
+        <v>32</v>
       </c>
-      <c r="F15" s="34" t="s">
-        <v>39</v>
+      <c r="I15" s="29">
+        <v>712</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="35">
+      <c r="J15" s="28">
         <v>8</v>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="28">
         <v>8</v>
       </c>
-      <c r="L15" s="36" t="s">
-        <v>40</v>
+      <c r="L15" s="48" t="s">
+        <v>42</v>
       </c>
-      <c r="M15" s="30"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="31"/>
+      <c r="M15" s="28">
+        <v>7</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="O15" s="26"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
@@ -1620,40 +1744,46 @@
     </row>
     <row r="16" spans="1:27" ht="21" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="33" t="s">
-        <v>41</v>
+      <c r="B16" s="27">
+        <v>144</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="C16" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="37">
-        <v>67008</v>
+      <c r="H16" s="29" t="s">
+        <v>34</v>
       </c>
-      <c r="F16" s="34" t="s">
+      <c r="I16" s="29">
+        <v>732</v>
+      </c>
+      <c r="J16" s="28">
+        <v>8</v>
+      </c>
+      <c r="K16" s="28">
+        <v>8</v>
+      </c>
+      <c r="L16" s="48" t="s">
+        <v>43</v>
+      </c>
+      <c r="M16" s="28">
+        <v>7</v>
+      </c>
+      <c r="N16" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16" s="37">
-        <v>712</v>
-      </c>
-      <c r="J16" s="38">
-        <v>8</v>
-      </c>
-      <c r="K16" s="38">
-        <v>20</v>
-      </c>
-      <c r="L16" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="M16" s="30"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
+      <c r="O16" s="26"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -1668,38 +1798,46 @@
     </row>
     <row r="17" spans="1:27" ht="21" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33" t="s">
-        <v>41</v>
+      <c r="B17" s="27">
+        <v>144</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="C17" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="H17" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="29">
+        <v>862</v>
+      </c>
+      <c r="J17" s="28">
+        <v>8</v>
+      </c>
+      <c r="K17" s="28">
+        <v>8</v>
+      </c>
+      <c r="L17" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="37" t="s">
-        <v>45</v>
+      <c r="M17" s="28">
+        <v>7</v>
       </c>
-      <c r="G17" s="37" t="s">
-        <v>26</v>
+      <c r="N17" s="47" t="s">
+        <v>47</v>
       </c>
-      <c r="H17" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="37">
-        <v>732</v>
-      </c>
-      <c r="J17" s="38">
-        <v>8</v>
-      </c>
-      <c r="K17" s="38">
-        <v>320</v>
-      </c>
-      <c r="L17" s="36"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
+      <c r="O17" s="26"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
@@ -1714,38 +1852,20 @@
     </row>
     <row r="18" spans="1:27" ht="21" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="I18" s="37">
-        <v>862</v>
-      </c>
-      <c r="J18" s="38">
-        <v>8</v>
-      </c>
-      <c r="K18" s="38">
-        <v>190</v>
-      </c>
-      <c r="L18" s="36"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="31"/>
-      <c r="O18" s="31"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="26"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -1760,20 +1880,20 @@
     </row>
     <row r="19" spans="1:27" ht="21" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="31"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="26"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -1788,20 +1908,20 @@
     </row>
     <row r="20" spans="1:27" ht="21" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="26"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -1816,20 +1936,20 @@
     </row>
     <row r="21" spans="1:27" ht="21" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="31"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="26"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
@@ -1844,20 +1964,20 @@
     </row>
     <row r="22" spans="1:27" ht="21" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="31"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="26"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -1872,20 +1992,20 @@
     </row>
     <row r="23" spans="1:27" ht="21" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="31"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="26"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -1898,22 +2018,22 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:27" ht="21" customHeight="1">
+    <row r="24" spans="1:27" ht="21" customHeight="1" thickBot="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="41"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="51"/>
+      <c r="O24" s="26"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -1926,7 +2046,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:27" ht="14.25" customHeight="1">
+    <row r="25" spans="1:27" ht="14.25" customHeight="1" thickBot="1">
       <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1958,19 +2078,19 @@
     <row r="26" spans="1:27" ht="18" customHeight="1">
       <c r="A26" s="1"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="44"/>
+      <c r="C26" s="33"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="45"/>
+      <c r="E26" s="34"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="46" t="s">
-        <v>48</v>
+      <c r="J26" s="35" t="s">
+        <v>36</v>
       </c>
-      <c r="K26" s="47">
+      <c r="K26" s="36">
         <f>SUM(K10:K24)</f>
-        <v>1608</v>
+        <v>514</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="5"/>
@@ -1992,13 +2112,14 @@
     <row r="27" spans="1:27" ht="21" customHeight="1">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="48" t="s">
-        <v>49</v>
+      <c r="C27" s="37" t="s">
+        <v>37</v>
       </c>
-      <c r="D27" s="49">
-        <v>259</v>
+      <c r="D27" s="38">
+        <f>SUM(M10:M24)</f>
+        <v>67</v>
       </c>
-      <c r="E27" s="45"/>
+      <c r="E27" s="34"/>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="K27" s="4"/>
@@ -2022,15 +2143,13 @@
     <row r="28" spans="1:27" ht="18" customHeight="1">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-      <c r="C28" s="50" t="s">
-        <v>50</v>
+      <c r="C28" s="39" t="s">
+        <v>38</v>
       </c>
-      <c r="D28" s="51">
-        <v>219</v>
-      </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
+      <c r="D28" s="40"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
       <c r="K28" s="4"/>
       <c r="L28" s="5"/>
       <c r="M28" s="1"/>
@@ -2055,8 +2174,8 @@
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
       <c r="K29" s="4"/>
       <c r="L29" s="5"/>
       <c r="M29" s="1"/>
@@ -30235,8 +30354,8 @@
       <c r="AA1000" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/docs/Packing Lists/Packing List Taller/Packing List Taller Exemple.xlsx
+++ b/docs/Packing Lists/Packing List Taller/Packing List Taller Exemple.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\system.PUNTOTRES\Documents\WORKSPACE\PackingListAutomation\docs\Packing Lists\Packing List Taller\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B5B208B-26A2-419B-B59E-F3879AE9CDB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440681D8-A075-4AAC-A256-8CF2944371EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="60">
   <si>
     <t>SWEET BAG SARL</t>
   </si>
@@ -314,14 +314,44 @@
 CAISSE</t>
   </si>
   <si>
-    <t>60X60X40</t>
-  </si>
-  <si>
     <t>POIDS BRUT
 CAISSE</t>
   </si>
   <si>
     <t>F67008</t>
+  </si>
+  <si>
+    <t>60x40x40</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>F67080</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EQ, COLOR ES </t>
+  </si>
+  <si>
+    <t>GAU</t>
+  </si>
+  <si>
+    <t>PXCEI-F67043</t>
+  </si>
+  <si>
+    <t>CAB</t>
+  </si>
+  <si>
+    <t>JPT</t>
+  </si>
+  <si>
+    <t>70</t>
   </si>
 </sst>
 </file>
@@ -1410,7 +1440,7 @@
         <v>18</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" s="44" t="s">
         <v>46</v>
@@ -1465,7 +1495,7 @@
         <v>10</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O10" s="26"/>
       <c r="P10" s="1"/>
@@ -1517,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O11" s="26"/>
       <c r="P11" s="1"/>
@@ -1569,7 +1599,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O12" s="26"/>
       <c r="P12" s="1"/>
@@ -1621,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O13" s="26"/>
       <c r="P13" s="1"/>
@@ -1673,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O14" s="26"/>
       <c r="P14" s="1"/>
@@ -1700,7 +1730,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15" s="29" t="s">
         <v>35</v>
@@ -1727,7 +1757,7 @@
         <v>7</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O15" s="26"/>
       <c r="P15" s="1"/>
@@ -1754,7 +1784,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F16" s="29" t="s">
         <v>33</v>
@@ -1781,7 +1811,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O16" s="26"/>
       <c r="P16" s="1"/>
@@ -1808,7 +1838,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" s="29" t="s">
         <v>33</v>
@@ -1835,7 +1865,7 @@
         <v>7</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O17" s="26"/>
       <c r="P17" s="1"/>
@@ -1853,18 +1883,42 @@
     <row r="18" spans="1:27" ht="21" customHeight="1">
       <c r="A18" s="1"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="28"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="48"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="49"/>
+      <c r="C18" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="29">
+        <v>863</v>
+      </c>
+      <c r="J18" s="28">
+        <v>8</v>
+      </c>
+      <c r="K18" s="28">
+        <v>8</v>
+      </c>
+      <c r="L18" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="28">
+        <v>7</v>
+      </c>
+      <c r="N18" s="47" t="s">
+        <v>49</v>
+      </c>
       <c r="O18" s="26"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
@@ -1881,21 +1935,49 @@
     <row r="19" spans="1:27" ht="21" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="49"/>
+      <c r="C19" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19" s="29">
+        <v>701</v>
+      </c>
+      <c r="J19" s="28">
+        <v>8</v>
+      </c>
+      <c r="K19" s="28">
+        <v>8</v>
+      </c>
+      <c r="L19" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="M19" s="28">
+        <v>7</v>
+      </c>
+      <c r="N19" s="47" t="s">
+        <v>49</v>
+      </c>
       <c r="O19" s="26"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="P19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -1909,18 +1991,42 @@
     <row r="20" spans="1:27" ht="21" customHeight="1">
       <c r="A20" s="1"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="48"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="49"/>
+      <c r="C20" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="29">
+        <v>688</v>
+      </c>
+      <c r="J20" s="28">
+        <v>8</v>
+      </c>
+      <c r="K20" s="28">
+        <v>600</v>
+      </c>
+      <c r="L20" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="M20" s="28">
+        <v>7</v>
+      </c>
+      <c r="N20" s="47" t="s">
+        <v>49</v>
+      </c>
       <c r="O20" s="26"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
@@ -2090,7 +2196,7 @@
       </c>
       <c r="K26" s="36">
         <f>SUM(K10:K24)</f>
-        <v>514</v>
+        <v>1130</v>
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="5"/>
@@ -2117,7 +2223,7 @@
       </c>
       <c r="D27" s="38">
         <f>SUM(M10:M24)</f>
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="18"/>
